--- a/document-parsing/evaluate/mineru_半导体场景模拟数据_解析benchmark评分.xlsx
+++ b/document-parsing/evaluate/mineru_半导体场景模拟数据_解析benchmark评分.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R404d6f6eae6145d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores" sheetId="2" r:id="Reaba1d5da4c94399"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimension Details" sheetId="3" r:id="R5bc18a89aa2b4c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R19e3811eaf1140f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores" sheetId="2" r:id="R935c711198fa482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimension Details" sheetId="3" r:id="R23739e0abfa14f7b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -251,7 +251,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="42">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -291,6 +291,15 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -493,10 +502,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42.220001220703125" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="52" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="112.11000061035156" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="9.109999656677246" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -553,9 +562,9 @@
       <x:c r="D5" s="13"/>
       <x:c r="E5" s="14"/>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="12" t="str">
-        <x:v>Average of per-file equal-weight scores</x:v>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="39" t="str">
+        <x:v>50-file avg of per-file dimension-equal scores</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
         <x:f>AVERAGE('Scores'!X2:X51)</x:f>
@@ -565,9 +574,9 @@
       <x:c r="D6" s="13"/>
       <x:c r="E6" s="14"/>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="12" t="str">
-        <x:v>Average of per-file count-weighted scores</x:v>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="39" t="str">
+        <x:v>50-file avg of per-file element-count-weighted scores</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
         <x:f>AVERAGE('Scores'!Y2:Y51)</x:f>
@@ -584,18 +593,18 @@
       <x:c r="D8" s="13"/>
       <x:c r="E8" s="14"/>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="17" t="str">
         <x:v>Dimension</x:v>
       </x:c>
       <x:c r="B9" s="18" t="str">
         <x:v>Files</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Equal-weight F1 avg</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>Count-weighted F1 avg</x:v>
+      <x:c r="C9" s="40" t="str">
+        <x:v>Per-dimension F1 avg across files</x:v>
+      </x:c>
+      <x:c r="D9" s="40" t="str">
+        <x:v>Per-dimension F1 weighted by all elements</x:v>
       </x:c>
       <x:c r="E9" s="19" t="str">
         <x:v>Total count</x:v>
@@ -798,12 +807,12 @@
     <x:col min="21" max="21" width="13.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="15.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="16.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="15.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="34" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="34" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="9.329999923706055" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="24" t="str">
         <x:v>File</x:v>
       </x:c>
@@ -873,11 +882,11 @@
       <x:c r="W1" s="25" t="str">
         <x:v>title_hierarchy count</x:v>
       </x:c>
-      <x:c r="X1" s="25" t="str">
-        <x:v>Equal-weight score</x:v>
-      </x:c>
-      <x:c r="Y1" s="25" t="str">
-        <x:v>Count-weighted score</x:v>
+      <x:c r="X1" s="41" t="str">
+        <x:v>Per-file dimension-equal score</x:v>
+      </x:c>
+      <x:c r="Y1" s="41" t="str">
+        <x:v>Per-file element-count-weighted score</x:v>
       </x:c>
       <x:c r="Z1" s="26" t="str">
         <x:v>Tool overall</x:v>
